--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>admin_pass</t>
+          <t>8c6976e5b5410415bde908bd4dee15dfb167a9c873fc4bb8a81f6f2ab448a918</t>
         </is>
       </c>
       <c r="D2" t="n">
